--- a/backend/expense_details.xlsx
+++ b/backend/expense_details.xlsx
@@ -415,21 +415,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Fast Food</v>
+        <v>Medicine</v>
       </c>
       <c r="B2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="C2" t="str">
-        <v>Food</v>
+        <v>Healthcare</v>
       </c>
       <c r="D2" t="str">
-        <v>12/6/2026</v>
+        <v>24/6/2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Snacks</v>
+        <v>Fast Food</v>
       </c>
       <c r="B3">
         <v>1500</v>
